--- a/ai_logs/Nguyen_Hoai_Nhi.AI_AuditLog_Template.xlsx
+++ b/ai_logs/Nguyen_Hoai_Nhi.AI_AuditLog_Template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Documents\GitHub\LAB211 - Nhom-5\ai_logs\Nguyễn Hoài Nhi AI_Log\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Documents\GitHub\LAB211-Nhom-5-\ai_logs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A04281F-57A3-4343-A2E2-25B445FA6856}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA79DE12-5FF6-4AEA-9F2C-8EE1E36458AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10245" yWindow="0" windowWidth="10245" windowHeight="10920" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Metadata &amp; Summary" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="259">
   <si>
     <t>AI AUDIT LOG - METADATA &amp; SUMMARY</t>
   </si>
@@ -671,6 +671,150 @@
   </si>
   <si>
     <t>UML Diagram</t>
+  </si>
+  <si>
+    <t>System Architecture</t>
+  </si>
+  <si>
+    <t>Implement EmployeeController, LeaveController, PayrollController, MainView, PayrollView, LeaveView, ReportView.</t>
+  </si>
+  <si>
+    <t>AI suggests adding more Controllers such as AuthController, DepartmentController, AttendanceController, SimulationController, along with Views following the MVC model.</t>
+  </si>
+  <si>
+    <t>ChatGPT conversation + Use Case Diagram</t>
+  </si>
+  <si>
+    <t>Critical Thinking: Some proposed AI Controllers are not included in the milestone requirements.
+Contextualization: Compare with the Use Case and instructor requirements.
+Creative Synthesis: Keep only EmployeeController, LeaveController, PayrollController, and the required Views.
+Decision: Remove unnecessary Controllers to avoid expanding the project scope.</t>
+  </si>
+  <si>
+    <t>It is necessary to identify the Controllers that need to be implemented for the project milestone.</t>
+  </si>
+  <si>
+    <t>Payroll</t>
+  </si>
+  <si>
+    <t>The payroll calculation function is designed according to the principles of polymorphism.</t>
+  </si>
+  <si>
+    <t>Implement PayrollController with NO_LOCK.</t>
+  </si>
+  <si>
+    <t>The AI ​​builds a PayrollController and calls employee.calculateSalary() to calculate the salary.</t>
+  </si>
+  <si>
+    <t>Critical Thinking: The controller should not contain a salary calculation formula.
+Contextualization: Compare OOP principles with the FullTimeEmployee and PartTimeEmployee classes.
+Creative Synthesis: Move all formulas to the calculateSalary() function of each subclass.
+Decision: The controller should only manage data and record the PayrollEntry.</t>
+  </si>
+  <si>
+    <t>PayrollController + Employee classes</t>
+  </si>
+  <si>
+    <t>Leave Management</t>
+  </si>
+  <si>
+    <t>It's necessary to understand the logic behind updating the number of days off.</t>
+  </si>
+  <si>
+    <t>Explain deductLeave(), addLeave(), checkRemaining().</t>
+  </si>
+  <si>
+    <t>AI explains the processing flow, validates, and updates the version.</t>
+  </si>
+  <si>
+    <t>Critical Thinking: Review each step of the usedLeaveDays and remainingLeaveDays updates. Contextualization: Compare with the LeaveBalance code. Creative Synthesis: Test valid and invalid cases. Decision: The appropriate logic should be retained.</t>
+  </si>
+  <si>
+    <t>LeaveBalance.java</t>
+  </si>
+  <si>
+    <t>MVC</t>
+  </si>
+  <si>
+    <t>Designing Console Interfaces Based on Use Cases</t>
+  </si>
+  <si>
+    <t>Implement MainView, PayrollView, LeaveView and ReportView.</t>
+  </si>
+  <si>
+    <t>AI suggests menus and MVC connection methods</t>
+  </si>
+  <si>
+    <t>Critical Thinking: The original menu did not match the Use Case. Contextualization: Compare with the Use Case Diagram. Creative Synthesis: Correct the 7 functional groups. Decision: Apply the revised version.</t>
+  </si>
+  <si>
+    <t>MainView + Use Case</t>
+  </si>
+  <si>
+    <t>CODE REVIEW</t>
+  </si>
+  <si>
+    <t>Architecture Review</t>
+  </si>
+  <si>
+    <t>Check the payroll logic settings.</t>
+  </si>
+  <si>
+    <t>Review code: no payroll logic in View/Controller.</t>
+  </si>
+  <si>
+    <t>AI suggests keeping all business logic in the Model.</t>
+  </si>
+  <si>
+    <t>Critical Thinking: Review the MVC principles. Contextualization: Compare the project structure. Creative Synthesis: Only the View displays, the Controller handles the execution. Decision: Architecture meets OOP and MVC requirements.</t>
+  </si>
+  <si>
+    <t>Source code</t>
+  </si>
+  <si>
+    <t>Scope Expansion</t>
+  </si>
+  <si>
+    <t>Requirement Mismatch</t>
+  </si>
+  <si>
+    <t>Architecture Suggestion</t>
+  </si>
+  <si>
+    <t>AI suggests adding AuthController, AttendanceController, and SimulationController.</t>
+  </si>
+  <si>
+    <t>The AI ​​designed the MainView with a menu that doesn't match the intended use case.</t>
+  </si>
+  <si>
+    <t>AI initially suggested placing some of the processing within the Controller.</t>
+  </si>
+  <si>
+    <t>Milestone only requires EmployeeController, LeaveController, and PayrollController.</t>
+  </si>
+  <si>
+    <t>The menu does not match the functions in the Use Case Diagram.</t>
+  </si>
+  <si>
+    <t>Business logic must be embedded within the Model according to the MVC/OOP principle.</t>
+  </si>
+  <si>
+    <t>Compare with the requirements document and Use Case.</t>
+  </si>
+  <si>
+    <t>Compare it to the Use Case diagram.</t>
+  </si>
+  <si>
+    <t>Review the architecture and compare the code.</t>
+  </si>
+  <si>
+    <t>Remove unnecessary controllers.</t>
+  </si>
+  <si>
+    <t>Revise the menu to meet the project requirements.</t>
+  </si>
+  <si>
+    <t>Move the payroll logic to the Employee classes.</t>
   </si>
 </sst>
 </file>
@@ -693,41 +837,48 @@
       <sz val="16"/>
       <color rgb="FF2E75B6"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
       <color rgb="FF2E75B6"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="9"/>
       <color rgb="FF666666"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="10"/>
       <color rgb="FF666666"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="16"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -735,26 +886,31 @@
       <sz val="10"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="10"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="5">
@@ -810,7 +966,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -847,6 +1003,7 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1176,14 +1333,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
     </row>
     <row r="3" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -1415,28 +1572,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
     </row>
     <row r="2" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="19"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
     </row>
     <row r="3" spans="1:8" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -1804,53 +1961,123 @@
     </row>
     <row r="17" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="7"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="7"/>
+      <c r="B17" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>216</v>
+      </c>
     </row>
     <row r="18" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="7"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
-      <c r="H18" s="7"/>
+      <c r="B18" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>224</v>
+      </c>
     </row>
     <row r="19" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="7"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
-      <c r="G19" s="7"/>
-      <c r="H19" s="7"/>
+      <c r="B19" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C19" s="18" t="s">
+        <v>225</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="H19" s="7" t="s">
+        <v>230</v>
+      </c>
     </row>
     <row r="20" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="7"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
-      <c r="G20" s="7"/>
-      <c r="H20" s="7"/>
+      <c r="B20" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="H20" s="7" t="s">
+        <v>236</v>
+      </c>
     </row>
     <row r="21" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="7"/>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
-      <c r="G21" s="7"/>
-      <c r="H21" s="7"/>
+      <c r="B21" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="G21" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>243</v>
+      </c>
     </row>
     <row r="22" spans="1:8" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="7"/>
@@ -1922,24 +2149,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="23" t="s">
         <v>70</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="22" t="s">
         <v>71</v>
       </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
     </row>
     <row r="3" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -2051,27 +2278,57 @@
     </row>
     <row r="9" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="7"/>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
+      <c r="B9" s="7" t="s">
+        <v>244</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>256</v>
+      </c>
     </row>
     <row r="10" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="7"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
+      <c r="B10" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>257</v>
+      </c>
     </row>
     <row r="11" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="7"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
+      <c r="B11" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>258</v>
+      </c>
     </row>
     <row r="12" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7"/>
@@ -2269,20 +2526,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="24" t="s">
         <v>102</v>
       </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
     </row>
     <row r="4" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
